--- a/excel/table.xlsx
+++ b/excel/table.xlsx
@@ -82,25 +82,7 @@
     <t xml:space="preserve">*Khajiit subtypes share the attitude table with default Khajiit</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">**</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Duadri share the table with Redguard</t>
-    </r>
+    <t xml:space="preserve">**Duadri share the table with Redguard</t>
   </si>
 </sst>
 </file>
@@ -111,7 +93,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -137,21 +119,17 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -259,53 +237,61 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -500,24 +486,24 @@
   <dimension ref="A1:R22"/>
   <sheetFormatPr defaultColWidth="8.3046875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="9.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="7.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="8.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="7.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="7.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="12.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="11.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="8.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="6.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="5.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="10.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="4.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="7.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="9.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="8.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="7.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="12.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="11.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="8.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="6.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="5.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="10.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="4.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="2" width="11.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="9.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="2" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="2" width="5.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="2" width="6.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="9.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="2" width="8.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="2" width="5.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="2" width="6.87"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1007,11 +993,15 @@
         <v>-5</v>
       </c>
       <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
+      <c r="K13" s="7" t="n">
+        <v>-5</v>
+      </c>
       <c r="L13" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="M13" s="7"/>
+      <c r="M13" s="7" t="n">
+        <v>-5</v>
+      </c>
       <c r="N13" s="7" t="n">
         <v>-10</v>
       </c>
@@ -1289,17 +1279,17 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="13" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0"/>
+    <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="17">
